--- a/sheets/민요/검수/양류가 (채보3).xlsx
+++ b/sheets/민요/검수/양류가 (채보3).xlsx
@@ -417,7 +417,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑仲/― 겹쳐</t>
+          <t xml:space="preserve">姑仲/– 겹쳐</t>
         </is>
       </c>
       <c r="K2" s="2"/>
@@ -689,7 +689,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑仲/― 겹쳐</t>
+          <t xml:space="preserve">姑仲/– 겹쳐</t>
         </is>
       </c>
       <c r="K5" s="2"/>
@@ -849,7 +849,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢/―無 겹쳐</t>
+          <t xml:space="preserve">潢/–無 겹쳐</t>
         </is>
       </c>
       <c r="K9" s="2"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢/―無</t>
+          <t xml:space="preserve">潢/–無</t>
         </is>
       </c>
       <c r="K10" s="2"/>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢/―無 겹쳐</t>
+          <t xml:space="preserve">潢/–無 겹쳐</t>
         </is>
       </c>
       <c r="K18" s="2"/>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑/― 겹쳐</t>
+          <t xml:space="preserve">仲姑/– 겹쳐</t>
         </is>
       </c>
       <c r="K19" s="2"/>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑/―潢 겹쳐</t>
+          <t xml:space="preserve">姑/–潢 겹쳐</t>
         </is>
       </c>
       <c r="K20" s="2"/>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">無/―姑 겹쳐</t>
+          <t xml:space="preserve">無/–姑 겹쳐</t>
         </is>
       </c>
       <c r="K21" s="2"/>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I24" s="2"/>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I28" s="2"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">無/―姑 겹쳐</t>
+          <t xml:space="preserve">無/–姑 겹쳐</t>
         </is>
       </c>
       <c r="K29" s="2"/>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I33" s="2"/>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I40" s="2"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑/― 겹쳐</t>
+          <t xml:space="preserve">仲姑/– 겹쳐</t>
         </is>
       </c>
       <c r="K43" s="2"/>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">無/―姑 겹쳐</t>
+          <t xml:space="preserve">無/–姑 겹쳐</t>
         </is>
       </c>
       <c r="K45" s="2"/>
@@ -2398,7 +2398,7 @@
       <c r="I48" s="3"/>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">無/―姑</t>
+          <t xml:space="preserve">無/–姑</t>
         </is>
       </c>
       <c r="K48" s="2"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">無/―姑 겹쳐</t>
+          <t xml:space="preserve">無/–姑 겹쳐</t>
         </is>
       </c>
       <c r="K54" s="2"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢/―無 겹쳐</t>
+          <t xml:space="preserve">潢/–無 겹쳐</t>
         </is>
       </c>
       <c r="K57" s="2"/>
@@ -2866,7 +2866,7 @@
       <c r="I60" s="3"/>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">無/―姑</t>
+          <t xml:space="preserve">無/–姑</t>
         </is>
       </c>
       <c r="K60" s="2"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑仲/― 겹쳐</t>
+          <t xml:space="preserve">姑仲/– 겹쳐</t>
         </is>
       </c>
       <c r="K62" s="2"/>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑仲/― 겹쳐</t>
+          <t xml:space="preserve">姑仲/– 겹쳐</t>
         </is>
       </c>
       <c r="K65" s="2"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢/―無 겹쳐</t>
+          <t xml:space="preserve">潢/–無 겹쳐</t>
         </is>
       </c>
       <c r="K69" s="2"/>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I76" s="2"/>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑/― 겹쳐</t>
+          <t xml:space="preserve">仲姑/– 겹쳐</t>
         </is>
       </c>
       <c r="K79" s="2"/>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑/―潢 겹쳐</t>
+          <t xml:space="preserve">姑/–潢 겹쳐</t>
         </is>
       </c>
       <c r="K80" s="2"/>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">無/―姑 겹쳐</t>
+          <t xml:space="preserve">無/–姑 겹쳐</t>
         </is>
       </c>
       <c r="K81" s="2"/>
@@ -3787,12 +3787,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I84" s="2"/>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲/―潢 겹쳐</t>
+          <t xml:space="preserve">仲/–潢 겹쳐</t>
         </is>
       </c>
       <c r="K97" s="2"/>
@@ -5642,7 +5642,7 @@
       <c r="I132" s="3"/>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢/―㳞 겹쳐</t>
+          <t xml:space="preserve">潢/–㳞 겹쳐</t>
         </is>
       </c>
       <c r="K132" s="2"/>
@@ -6855,7 +6855,7 @@
       <c r="G5" s="10"/>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="10"/>
@@ -6873,13 +6873,13 @@
       <c r="M5" s="10"/>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O5" s="10"/>
       <c r="P5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q5" s="10"/>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="P10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="Q10" s="9"/>
@@ -7539,7 +7539,7 @@
       <c r="G13" s="12"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="9"/>
@@ -7563,13 +7563,13 @@
       <c r="O13" s="12"/>
       <c r="P13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="S13" s="9"/>

--- a/sheets/민요/검수/양류가 (채보3).xlsx
+++ b/sheets/민요/검수/양류가 (채보3).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6618,129 +6659,129 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">양류가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">제비</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">앙</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아리</t>
         </is>
       </c>
-      <c r="L3" s="18" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
       </c>
-      <c r="N3" s="18" t="inlineStr">
+      <c r="N3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">십리</t>
         </is>
       </c>
-      <c r="P3" s="18" t="inlineStr">
+      <c r="P3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="R3" s="18" t="inlineStr">
+      <c r="R3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="S3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="T3" s="18" t="inlineStr">
+      <c r="T3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="U3" s="11" t="inlineStr">
+      <c r="U3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아리</t>
         </is>
@@ -6748,86 +6789,86 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">맏</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="I4" s="25"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K4" s="25"/>
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="18" t="inlineStr">
+      <c r="M4" s="25"/>
+      <c r="N4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O4" s="12" t="inlineStr">
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="P4" s="18" t="inlineStr">
+      <c r="P4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q4" s="12" t="inlineStr">
+      <c r="Q4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">릴</t>
         </is>
       </c>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U4" s="9" t="inlineStr">
+      <c r="S4" s="25"/>
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -6835,165 +6876,165 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="27"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="27"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="27"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="27"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="27"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="O5" s="27"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="Q5" s="27"/>
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S5" s="10"/>
-      <c r="T5" s="17" t="inlineStr">
+      <c r="S5" s="27"/>
+      <c r="T5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U5" s="10"/>
+      <c r="U5" s="27"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쫑</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">역이</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아리</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
       </c>
-      <c r="N6" s="18" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="P6" s="18" t="inlineStr">
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="R6" s="18" t="inlineStr">
+      <c r="R6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="S6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="T6" s="18" t="inlineStr">
+      <c r="T6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="U6" s="11" t="inlineStr">
+      <c r="U6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아리</t>
         </is>
@@ -7001,90 +7042,90 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">것이</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="26"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="18" t="inlineStr">
+      <c r="I7" s="25"/>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K7" s="25"/>
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M7" s="12" t="inlineStr">
+      <c r="M7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="N7" s="18" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O7" s="12" t="inlineStr">
+      <c r="O7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="P7" s="18" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="Q7" s="12" t="inlineStr">
+      <c r="Q7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">병</t>
         </is>
       </c>
-      <c r="R7" s="18" t="inlineStr">
+      <c r="R7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="S7" s="12" t="inlineStr">
+      <c r="S7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="T7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U7" s="9" t="inlineStr">
+      <c r="T7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
@@ -7092,181 +7133,181 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">山</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">때들석</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="18" t="inlineStr">
+      <c r="K8" s="28"/>
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="M8" s="13" t="inlineStr">
+      <c r="M8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="N8" s="18" t="inlineStr">
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="P8" s="18" t="inlineStr">
+      <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="Q8" s="13" t="inlineStr">
+      <c r="Q8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">시는</t>
         </is>
       </c>
-      <c r="R8" s="18" t="inlineStr">
+      <c r="R8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="S8" s="13" t="inlineStr">
+      <c r="S8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">넘겨</t>
         </is>
       </c>
-      <c r="T8" s="18" t="inlineStr">
+      <c r="T8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U8" s="13"/>
+      <c r="U8" s="28"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">앉</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">휴</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">앉</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아라리</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="M9" s="22"/>
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="18" t="inlineStr">
+      <c r="O9" s="24"/>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="S9" s="11" t="inlineStr">
+      <c r="S9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="T9" s="17" t="inlineStr">
+      <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
+      <c r="U9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아라리</t>
         </is>
@@ -7274,94 +7315,94 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="C10" s="26"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고서</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">린다</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="N10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="O10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="18" t="inlineStr">
+      <c r="Q10" s="25"/>
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="S10" s="12" t="inlineStr">
+      <c r="S10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="T10" s="18" t="inlineStr">
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="U10" s="12" t="inlineStr">
+      <c r="U10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -7369,78 +7410,78 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E11" s="27"/>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G11" s="27"/>
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑仲</t>
         </is>
       </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="28"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M11" s="27"/>
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑無</t>
         </is>
       </c>
-      <c r="O11" s="13" t="inlineStr">
+      <c r="O11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">병</t>
         </is>
       </c>
-      <c r="P11" s="18" t="inlineStr">
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="18" t="inlineStr">
+      <c r="Q11" s="28"/>
+      <c r="R11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑仲</t>
         </is>
       </c>
-      <c r="S11" s="13" t="inlineStr">
+      <c r="S11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="T11" s="18" t="inlineStr">
+      <c r="T11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U11" s="13" t="inlineStr">
+      <c r="U11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -7448,297 +7489,297 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사랑</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S12" s="8"/>
-      <c r="T12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U12" s="8"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O12" s="22"/>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S12" s="22"/>
+      <c r="T12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢</t>
         </is>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="C13" s="26"/>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢</t>
         </is>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="E13" s="26"/>
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="26"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="18" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="18" t="inlineStr">
+      <c r="M13" s="26"/>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="O13" s="12"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="26"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="Q13" s="25"/>
+      <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="S13" s="9"/>
-      <c r="T13" s="17" t="inlineStr">
+      <c r="S13" s="25"/>
+      <c r="T13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U13" s="9"/>
+      <c r="U13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="C14" s="28"/>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E14" s="28"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲潢</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">꼬려</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="R14" s="18" t="inlineStr">
+      <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="S14" s="13" t="inlineStr">
+      <c r="S14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="T14" s="17" t="inlineStr">
+      <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="U14" s="10"/>
+      <c r="U14" s="27"/>
     </row>
     <row r="15">
       <c r="A15" s="0"/>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">양류가</t>
         </is>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">앙</t>
         </is>
       </c>
-      <c r="R17" s="18" t="inlineStr">
+      <c r="R17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="S17" s="11" t="inlineStr">
+      <c r="S17" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">양</t>
         </is>
       </c>
-      <c r="T17" s="17" t="inlineStr">
+      <c r="T17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="U17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -7746,194 +7787,194 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="B18" s="21"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="17" t="inlineStr">
+      <c r="Q18" s="25"/>
+      <c r="R18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S18" s="9"/>
-      <c r="T18" s="18" t="inlineStr">
+      <c r="S18" s="25"/>
+      <c r="T18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="U18" s="12"/>
+      <c r="U18" s="26"/>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="0"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="17" t="inlineStr">
+      <c r="B19" s="21"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q19" s="27"/>
+      <c r="R19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S19" s="10"/>
-      <c r="T19" s="17" t="inlineStr">
+      <c r="S19" s="27"/>
+      <c r="T19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="U19" s="10"/>
+      <c r="U19" s="27"/>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="0"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q20" s="8" t="inlineStr">
+      <c r="B20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q20" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">류</t>
         </is>
       </c>
-      <c r="R20" s="18" t="inlineStr">
+      <c r="R20" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="S20" s="11" t="inlineStr">
+      <c r="S20" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">류</t>
         </is>
       </c>
-      <c r="T20" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U20" s="8"/>
+      <c r="T20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U20" s="22"/>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="0"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="17" t="inlineStr">
+      <c r="B21" s="21"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S21" s="9"/>
-      <c r="T21" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U21" s="9"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U21" s="25"/>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="0"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q22" s="10" t="inlineStr">
+      <c r="B22" s="21"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q22" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="R22" s="18" t="inlineStr">
+      <c r="R22" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="S22" s="13" t="inlineStr">
+      <c r="S22" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="T22" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U22" s="10" t="inlineStr">
+      <c r="T22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U22" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -7941,38 +7982,38 @@
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="0"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="18" t="inlineStr">
+      <c r="B23" s="21"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="21"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="21"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S23" s="11"/>
-      <c r="T23" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
+      <c r="S23" s="24"/>
+      <c r="T23" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U23" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
@@ -7980,186 +8021,186 @@
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="0"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="18" t="inlineStr">
+      <c r="B24" s="21"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S24" s="12"/>
-      <c r="T24" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U24" s="9"/>
+      <c r="S24" s="26"/>
+      <c r="T24" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U24" s="25"/>
     </row>
     <row r="25" ht="56" customHeight="1">
       <c r="A25" s="0"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="18" t="inlineStr">
+      <c r="B25" s="21"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="27"/>
+      <c r="P25" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q25" s="27"/>
+      <c r="R25" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑潢</t>
         </is>
       </c>
-      <c r="S25" s="13"/>
-      <c r="T25" s="18" t="inlineStr">
+      <c r="S25" s="28"/>
+      <c r="T25" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U25" s="13"/>
+      <c r="U25" s="28"/>
     </row>
     <row r="26" ht="56" customHeight="1">
       <c r="A26" s="0"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q26" s="8" t="inlineStr">
+      <c r="B26" s="21"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q26" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="R26" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S26" s="8" t="inlineStr">
+      <c r="R26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S26" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="T26" s="18" t="inlineStr">
+      <c r="T26" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U26" s="11"/>
+      <c r="U26" s="24"/>
     </row>
     <row r="27" ht="56" customHeight="1">
       <c r="A27" s="0"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="17" t="inlineStr">
+      <c r="B27" s="21"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="17" t="inlineStr">
+      <c r="Q27" s="25"/>
+      <c r="R27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S27" s="9"/>
-      <c r="T27" s="18" t="inlineStr">
+      <c r="S27" s="25"/>
+      <c r="T27" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢㳞</t>
         </is>
       </c>
-      <c r="U27" s="12"/>
+      <c r="U27" s="26"/>
     </row>
     <row r="28" ht="56" customHeight="1">
       <c r="A28" s="0"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="17" t="inlineStr">
+      <c r="B28" s="21"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="27"/>
+      <c r="P28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="17" t="inlineStr">
+      <c r="Q28" s="27"/>
+      <c r="R28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S28" s="10"/>
-      <c r="T28" s="18" t="inlineStr">
+      <c r="S28" s="27"/>
+      <c r="T28" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U28" s="13"/>
+      <c r="U28" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/sheets/민요/검수/양류가 (채보3).xlsx
+++ b/sheets/민요/검수/양류가 (채보3).xlsx
@@ -6632,32 +6632,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="29.14" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="29.14" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6787,11 +6787,11 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="29.14" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
@@ -6874,7 +6874,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="29.14" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6902,13 +6902,13 @@
       <c r="I5" s="27"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K5" s="27"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="27"/>
@@ -6926,18 +6926,18 @@
       <c r="Q5" s="27"/>
       <c r="R5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S5" s="27"/>
       <c r="T5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U5" s="27"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="29.14" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="29.14" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="29.14" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K8" s="28"/>
@@ -7221,12 +7221,12 @@
       </c>
       <c r="T8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U8" s="28"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="29.14" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="29.14" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="29.14" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="29.14" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="29.14" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
       <c r="I13" s="25"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="25"/>
@@ -7616,12 +7616,12 @@
       <c r="S13" s="25"/>
       <c r="T13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="29.14" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
     <row r="15">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="29.14" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="29.14" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="29.14" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="25"/>
@@ -7803,7 +7803,7 @@
       <c r="O18" s="25"/>
       <c r="P18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q18" s="25"/>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="U18" s="26"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="29.14" customHeight="1">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="27"/>
@@ -7844,7 +7844,7 @@
       <c r="Q19" s="27"/>
       <c r="R19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S19" s="27"/>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="U19" s="27"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="29.14" customHeight="1">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="29.14" customHeight="1">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="U21" s="25"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="29.14" customHeight="1">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="27"/>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="29.14" customHeight="1">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="29.14" customHeight="1">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="25"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="U24" s="25"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="29.14" customHeight="1">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="27"/>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="U25" s="28"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="29.14" customHeight="1">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="U26" s="24"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="29.14" customHeight="1">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="25"/>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="U27" s="26"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="29.14" customHeight="1">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="27"/>

--- a/sheets/민요/검수/양류가 (채보3).xlsx
+++ b/sheets/민요/검수/양류가 (채보3).xlsx
@@ -1517,7 +1517,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J37" s="4"/>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J49" s="4"/>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J61" s="4"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="G14" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="M14" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O14" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P14" s="21" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="Q14" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R14" s="23" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="S14" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="T14" s="21" t="inlineStr">

--- a/sheets/민요/검수/양류가 (채보3).xlsx
+++ b/sheets/민요/검수/양류가 (채보3).xlsx
@@ -6657,7 +6657,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="29.14" customHeight="1">
+    <row r="2" ht="43.99" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="29.14" customHeight="1">
+    <row r="3" ht="43.99" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6713,7 +6713,8 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">제비</t>
+          <t xml:space="preserve">제
+비</t>
         </is>
       </c>
       <c r="H3" s="23" t="inlineStr">
@@ -6733,7 +6734,8 @@
       </c>
       <c r="K3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리</t>
+          <t xml:space="preserve">아
+리</t>
         </is>
       </c>
       <c r="L3" s="23" t="inlineStr">
@@ -6753,7 +6755,8 @@
       </c>
       <c r="O3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">십리</t>
+          <t xml:space="preserve">십
+리</t>
         </is>
       </c>
       <c r="P3" s="23" t="inlineStr">
@@ -6783,11 +6786,12 @@
       </c>
       <c r="U3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="29.14" customHeight="1">
+          <t xml:space="preserve">아
+리</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="43.99" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6874,7 +6878,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="29.14" customHeight="1">
+    <row r="5" ht="43.99" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6937,7 +6941,7 @@
       </c>
       <c r="U5" s="27"/>
     </row>
-    <row r="6" ht="29.14" customHeight="1">
+    <row r="6" ht="43.99" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6966,7 +6970,8 @@
       </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">역이</t>
+          <t xml:space="preserve">역
+이</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -6986,7 +6991,8 @@
       </c>
       <c r="K6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리</t>
+          <t xml:space="preserve">아
+리</t>
         </is>
       </c>
       <c r="L6" s="23" t="inlineStr">
@@ -7036,11 +7042,12 @@
       </c>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="29.14" customHeight="1">
+          <t xml:space="preserve">아
+리</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="43.99" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -7049,7 +7056,8 @@
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">것이</t>
+          <t xml:space="preserve">것
+이</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -7131,7 +7139,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="29.14" customHeight="1">
+    <row r="8" ht="43.99" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -7150,7 +7158,9 @@
       </c>
       <c r="E8" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">때들석</t>
+          <t xml:space="preserve">때
+들
+석</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -7206,7 +7216,8 @@
       </c>
       <c r="Q8" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">시는</t>
+          <t xml:space="preserve">시
+는</t>
         </is>
       </c>
       <c r="R8" s="23" t="inlineStr">
@@ -7216,7 +7227,8 @@
       </c>
       <c r="S8" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">넘겨</t>
+          <t xml:space="preserve">넘
+겨</t>
         </is>
       </c>
       <c r="T8" s="23" t="inlineStr">
@@ -7226,7 +7238,7 @@
       </c>
       <c r="U8" s="28"/>
     </row>
-    <row r="9" ht="29.14" customHeight="1">
+    <row r="9" ht="43.99" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -7271,7 +7283,9 @@
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">아라리</t>
+          <t xml:space="preserve">아
+라
+리</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -7309,11 +7323,13 @@
       </c>
       <c r="U9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">아라리</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="29.14" customHeight="1">
+          <t xml:space="preserve">아
+라
+리</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="43.99" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -7328,7 +7344,8 @@
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">고서</t>
+          <t xml:space="preserve">고
+서</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -7338,7 +7355,8 @@
       </c>
       <c r="G10" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">린다</t>
+          <t xml:space="preserve">린
+다</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -7408,7 +7426,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="29.14" customHeight="1">
+    <row r="11" ht="43.99" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -7487,7 +7505,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="29.14" customHeight="1">
+    <row r="12" ht="43.99" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -7496,7 +7514,8 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">사랑</t>
+          <t xml:space="preserve">사
+랑</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -7558,7 +7577,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="29.14" customHeight="1">
+    <row r="13" ht="43.99" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -7621,7 +7640,7 @@
       </c>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="29.14" customHeight="1">
+    <row r="14" ht="43.99" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -7652,7 +7671,8 @@
       </c>
       <c r="I14" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">꼬려</t>
+          <t xml:space="preserve">꼬
+려</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -7711,7 +7731,7 @@
     <row r="15">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="29.14" customHeight="1">
+    <row r="16" ht="43.99" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -7738,7 +7758,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="29.14" customHeight="1">
+    <row r="17" ht="43.99" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -7785,7 +7805,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="29.14" customHeight="1">
+    <row r="18" ht="43.99" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="25"/>
@@ -7820,7 +7840,7 @@
       </c>
       <c r="U18" s="26"/>
     </row>
-    <row r="19" ht="29.14" customHeight="1">
+    <row r="19" ht="43.99" customHeight="1">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="27"/>
@@ -7855,7 +7875,7 @@
       </c>
       <c r="U19" s="27"/>
     </row>
-    <row r="20" ht="29.14" customHeight="1">
+    <row r="20" ht="43.99" customHeight="1">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -7898,7 +7918,7 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="29.14" customHeight="1">
+    <row r="21" ht="43.99" customHeight="1">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
@@ -7933,7 +7953,7 @@
       </c>
       <c r="U21" s="25"/>
     </row>
-    <row r="22" ht="29.14" customHeight="1">
+    <row r="22" ht="43.99" customHeight="1">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="27"/>
@@ -7980,7 +8000,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="29.14" customHeight="1">
+    <row r="23" ht="43.99" customHeight="1">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -8019,7 +8039,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="29.14" customHeight="1">
+    <row r="24" ht="43.99" customHeight="1">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="25"/>
@@ -8054,7 +8074,7 @@
       </c>
       <c r="U24" s="25"/>
     </row>
-    <row r="25" ht="29.14" customHeight="1">
+    <row r="25" ht="43.99" customHeight="1">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="27"/>
@@ -8089,7 +8109,7 @@
       </c>
       <c r="U25" s="28"/>
     </row>
-    <row r="26" ht="29.14" customHeight="1">
+    <row r="26" ht="43.99" customHeight="1">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -8132,7 +8152,7 @@
       </c>
       <c r="U26" s="24"/>
     </row>
-    <row r="27" ht="29.14" customHeight="1">
+    <row r="27" ht="43.99" customHeight="1">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="25"/>
@@ -8167,7 +8187,7 @@
       </c>
       <c r="U27" s="26"/>
     </row>
-    <row r="28" ht="29.14" customHeight="1">
+    <row r="28" ht="43.99" customHeight="1">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="27"/>

--- a/sheets/민요/검수/양류가 (채보3).xlsx
+++ b/sheets/민요/검수/양류가 (채보3).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6691,7 +6714,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -6701,7 +6724,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -6711,7 +6734,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">제
 비</t>
@@ -6722,7 +6745,7 @@
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">앙</t>
         </is>
@@ -6732,7 +6755,7 @@
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 리</t>
@@ -6743,7 +6766,7 @@
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
@@ -6753,7 +6776,7 @@
           <t xml:space="preserve">南潢</t>
         </is>
       </c>
-      <c r="O3" s="24" t="inlineStr">
+      <c r="O3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">십
 리</t>
@@ -6764,7 +6787,7 @@
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="Q3" s="24" t="inlineStr">
+      <c r="Q3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -6774,7 +6797,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S3" s="24" t="inlineStr">
+      <c r="S3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -6784,7 +6807,7 @@
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="U3" s="24" t="inlineStr">
+      <c r="U3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 리</t>
@@ -6798,7 +6821,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -6808,7 +6831,7 @@
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -6818,7 +6841,7 @@
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">맏</t>
         </is>
@@ -6828,25 +6851,25 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="31"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K4" s="25"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M4" s="25"/>
+      <c r="M4" s="31"/>
       <c r="N4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O4" s="26" t="inlineStr">
+      <c r="O4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -6856,7 +6879,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q4" s="26" t="inlineStr">
+      <c r="Q4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">릴</t>
         </is>
@@ -6866,13 +6889,13 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S4" s="25"/>
+      <c r="S4" s="31"/>
       <c r="T4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U4" s="25" t="inlineStr">
+      <c r="U4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -6885,61 +6908,61 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="33"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="27"/>
+      <c r="I5" s="33"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="27"/>
+      <c r="K5" s="33"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="27"/>
+      <c r="M5" s="33"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="27"/>
+      <c r="O5" s="33"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q5" s="27"/>
+      <c r="Q5" s="33"/>
       <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S5" s="27"/>
+      <c r="S5" s="33"/>
       <c r="T5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U5" s="27"/>
+      <c r="U5" s="33"/>
     </row>
     <row r="6" ht="43.99" customHeight="1">
       <c r="A6" s="0"/>
@@ -6948,7 +6971,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -6958,7 +6981,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">쫑</t>
         </is>
@@ -6968,7 +6991,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">역
 이</t>
@@ -6979,7 +7002,7 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -6989,7 +7012,7 @@
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="K6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 리</t>
@@ -7000,7 +7023,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="M6" s="24" t="inlineStr">
+      <c r="M6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
@@ -7010,7 +7033,7 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="O6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
@@ -7020,7 +7043,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="Q6" s="24" t="inlineStr">
+      <c r="Q6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -7030,7 +7053,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S6" s="24" t="inlineStr">
+      <c r="S6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -7040,7 +7063,7 @@
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="U6" s="24" t="inlineStr">
+      <c r="U6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 리</t>
@@ -7054,7 +7077,7 @@
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">것
 이</t>
@@ -7065,7 +7088,7 @@
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -7075,25 +7098,25 @@
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="G7" s="26"/>
+      <c r="G7" s="32"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I7" s="25"/>
+      <c r="I7" s="31"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K7" s="25"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M7" s="26" t="inlineStr">
+      <c r="M7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -7103,7 +7126,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O7" s="26" t="inlineStr">
+      <c r="O7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -7113,7 +7136,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="Q7" s="26" t="inlineStr">
+      <c r="Q7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">병</t>
         </is>
@@ -7123,7 +7146,7 @@
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="S7" s="26" t="inlineStr">
+      <c r="S7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
@@ -7133,7 +7156,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U7" s="25" t="inlineStr">
+      <c r="U7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
@@ -7146,7 +7169,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">山</t>
         </is>
@@ -7156,7 +7179,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">때
 들
@@ -7168,7 +7191,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -7178,7 +7201,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="I8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -7188,13 +7211,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K8" s="28"/>
+      <c r="K8" s="34"/>
       <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="M8" s="28" t="inlineStr">
+      <c r="M8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -7204,7 +7227,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="O8" s="28" t="inlineStr">
+      <c r="O8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -7214,7 +7237,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="Q8" s="28" t="inlineStr">
+      <c r="Q8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">시
 는</t>
@@ -7225,7 +7248,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="S8" s="28" t="inlineStr">
+      <c r="S8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">넘
 겨</t>
@@ -7236,7 +7259,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U8" s="28"/>
+      <c r="U8" s="34"/>
     </row>
     <row r="9" ht="43.99" customHeight="1">
       <c r="A9" s="0"/>
@@ -7245,13 +7268,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">앉</t>
         </is>
@@ -7261,7 +7284,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">휴</t>
         </is>
@@ -7271,7 +7294,7 @@
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">앉</t>
         </is>
@@ -7281,7 +7304,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 라
@@ -7293,25 +7316,25 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="22"/>
+      <c r="M9" s="29"/>
       <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="24"/>
+      <c r="O9" s="30"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q9" s="22"/>
+      <c r="Q9" s="29"/>
       <c r="R9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="S9" s="24" t="inlineStr">
+      <c r="S9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
@@ -7321,7 +7344,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U9" s="22" t="inlineStr">
+      <c r="U9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 라
@@ -7336,13 +7359,13 @@
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="C10" s="26"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">고
 서</t>
@@ -7353,7 +7376,7 @@
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">린
 다</t>
@@ -7364,7 +7387,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="I10" s="26" t="inlineStr">
+      <c r="I10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -7374,7 +7397,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -7384,7 +7407,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="M10" s="26" t="inlineStr">
+      <c r="M10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -7394,7 +7417,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="O10" s="26" t="inlineStr">
+      <c r="O10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
@@ -7404,13 +7427,13 @@
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="Q10" s="25"/>
+      <c r="Q10" s="31"/>
       <c r="R10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="S10" s="26" t="inlineStr">
+      <c r="S10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -7420,7 +7443,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="U10" s="26" t="inlineStr">
+      <c r="U10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -7433,31 +7456,31 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E11" s="27"/>
+      <c r="E11" s="33"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑仲</t>
         </is>
       </c>
-      <c r="I11" s="28"/>
+      <c r="I11" s="34"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K11" s="27" t="inlineStr">
+      <c r="K11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -7467,13 +7490,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M11" s="27"/>
+      <c r="M11" s="33"/>
       <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑無</t>
         </is>
       </c>
-      <c r="O11" s="28" t="inlineStr">
+      <c r="O11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">병</t>
         </is>
@@ -7483,13 +7506,13 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="Q11" s="28"/>
+      <c r="Q11" s="34"/>
       <c r="R11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑仲</t>
         </is>
       </c>
-      <c r="S11" s="28" t="inlineStr">
+      <c r="S11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -7499,7 +7522,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U11" s="28" t="inlineStr">
+      <c r="U11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -7512,7 +7535,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">사
 랑</t>
@@ -7523,19 +7546,19 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="29"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
@@ -7545,37 +7568,37 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K12" s="22"/>
+      <c r="K12" s="29"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M12" s="22"/>
+      <c r="M12" s="29"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="22"/>
+      <c r="O12" s="29"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q12" s="22"/>
+      <c r="Q12" s="29"/>
       <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S12" s="22"/>
+      <c r="S12" s="29"/>
       <c r="T12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U12" s="22"/>
+      <c r="U12" s="29"/>
     </row>
     <row r="13" ht="43.99" customHeight="1">
       <c r="A13" s="0"/>
@@ -7584,61 +7607,61 @@
           <t xml:space="preserve">汰潢</t>
         </is>
       </c>
-      <c r="C13" s="26"/>
+      <c r="C13" s="32"/>
       <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢</t>
         </is>
       </c>
-      <c r="E13" s="26"/>
+      <c r="E13" s="32"/>
       <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="32"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="M13" s="26"/>
+      <c r="M13" s="32"/>
       <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="O13" s="26"/>
+      <c r="O13" s="32"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="31"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="S13" s="25"/>
+      <c r="S13" s="31"/>
       <c r="T13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U13" s="25"/>
+      <c r="U13" s="31"/>
     </row>
     <row r="14" ht="43.99" customHeight="1">
       <c r="A14" s="0"/>
@@ -7647,19 +7670,19 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C14" s="28"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E14" s="28"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲潢</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7669,7 +7692,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="I14" s="28" t="inlineStr">
+      <c r="I14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">꼬
 려</t>
@@ -7680,13 +7703,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="M14" s="27" t="inlineStr">
+      <c r="M14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7696,7 +7719,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="O14" s="27" t="inlineStr">
+      <c r="O14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7706,7 +7729,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="Q14" s="27" t="inlineStr">
+      <c r="Q14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7716,7 +7739,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="S14" s="28" t="inlineStr">
+      <c r="S14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7726,7 +7749,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="U14" s="27"/>
+      <c r="U14" s="33"/>
     </row>
     <row r="15">
       <c r="A15" s="0"/>
@@ -7761,25 +7784,25 @@
     <row r="17" ht="43.99" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
-      <c r="C17" s="22"/>
+      <c r="C17" s="29"/>
       <c r="D17" s="21"/>
-      <c r="E17" s="22"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="21"/>
-      <c r="G17" s="22"/>
+      <c r="G17" s="29"/>
       <c r="H17" s="21"/>
-      <c r="I17" s="22"/>
+      <c r="I17" s="29"/>
       <c r="J17" s="21"/>
-      <c r="K17" s="22"/>
+      <c r="K17" s="29"/>
       <c r="L17" s="21"/>
-      <c r="M17" s="22"/>
+      <c r="M17" s="29"/>
       <c r="N17" s="21"/>
-      <c r="O17" s="22"/>
+      <c r="O17" s="29"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q17" s="22" t="inlineStr">
+      <c r="Q17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">앙</t>
         </is>
@@ -7789,7 +7812,7 @@
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="S17" s="24" t="inlineStr">
+      <c r="S17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">양</t>
         </is>
@@ -7799,7 +7822,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="U17" s="22" t="inlineStr">
+      <c r="U17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -7808,95 +7831,95 @@
     <row r="18" ht="43.99" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
-      <c r="C18" s="25"/>
+      <c r="C18" s="31"/>
       <c r="D18" s="21"/>
-      <c r="E18" s="25"/>
+      <c r="E18" s="31"/>
       <c r="F18" s="21"/>
-      <c r="G18" s="25"/>
+      <c r="G18" s="31"/>
       <c r="H18" s="21"/>
-      <c r="I18" s="25"/>
+      <c r="I18" s="31"/>
       <c r="J18" s="21"/>
-      <c r="K18" s="25"/>
+      <c r="K18" s="31"/>
       <c r="L18" s="21"/>
-      <c r="M18" s="25"/>
+      <c r="M18" s="31"/>
       <c r="N18" s="21"/>
-      <c r="O18" s="25"/>
+      <c r="O18" s="31"/>
       <c r="P18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q18" s="25"/>
+      <c r="Q18" s="31"/>
       <c r="R18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S18" s="25"/>
+      <c r="S18" s="31"/>
       <c r="T18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="U18" s="26"/>
+      <c r="U18" s="32"/>
     </row>
     <row r="19" ht="43.99" customHeight="1">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
-      <c r="C19" s="27"/>
+      <c r="C19" s="33"/>
       <c r="D19" s="21"/>
-      <c r="E19" s="27"/>
+      <c r="E19" s="33"/>
       <c r="F19" s="21"/>
-      <c r="G19" s="27"/>
+      <c r="G19" s="33"/>
       <c r="H19" s="21"/>
-      <c r="I19" s="27"/>
+      <c r="I19" s="33"/>
       <c r="J19" s="21"/>
-      <c r="K19" s="27"/>
+      <c r="K19" s="33"/>
       <c r="L19" s="21"/>
-      <c r="M19" s="27"/>
+      <c r="M19" s="33"/>
       <c r="N19" s="21"/>
-      <c r="O19" s="27"/>
+      <c r="O19" s="33"/>
       <c r="P19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q19" s="27"/>
+      <c r="Q19" s="33"/>
       <c r="R19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S19" s="27"/>
+      <c r="S19" s="33"/>
       <c r="T19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="U19" s="27"/>
+      <c r="U19" s="33"/>
     </row>
     <row r="20" ht="43.99" customHeight="1">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
-      <c r="C20" s="22"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="21"/>
-      <c r="E20" s="22"/>
+      <c r="E20" s="29"/>
       <c r="F20" s="21"/>
-      <c r="G20" s="22"/>
+      <c r="G20" s="29"/>
       <c r="H20" s="21"/>
-      <c r="I20" s="22"/>
+      <c r="I20" s="29"/>
       <c r="J20" s="21"/>
-      <c r="K20" s="22"/>
+      <c r="K20" s="29"/>
       <c r="L20" s="21"/>
-      <c r="M20" s="22"/>
+      <c r="M20" s="29"/>
       <c r="N20" s="21"/>
-      <c r="O20" s="22"/>
+      <c r="O20" s="29"/>
       <c r="P20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q20" s="22" t="inlineStr">
+      <c r="Q20" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">류</t>
         </is>
@@ -7906,7 +7929,7 @@
           <t xml:space="preserve">姑潢</t>
         </is>
       </c>
-      <c r="S20" s="24" t="inlineStr">
+      <c r="S20" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">류</t>
         </is>
@@ -7916,65 +7939,65 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U20" s="22"/>
+      <c r="U20" s="29"/>
     </row>
     <row r="21" ht="43.99" customHeight="1">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
-      <c r="C21" s="25"/>
+      <c r="C21" s="31"/>
       <c r="D21" s="21"/>
-      <c r="E21" s="25"/>
+      <c r="E21" s="31"/>
       <c r="F21" s="21"/>
-      <c r="G21" s="25"/>
+      <c r="G21" s="31"/>
       <c r="H21" s="21"/>
-      <c r="I21" s="25"/>
+      <c r="I21" s="31"/>
       <c r="J21" s="21"/>
-      <c r="K21" s="25"/>
+      <c r="K21" s="31"/>
       <c r="L21" s="21"/>
-      <c r="M21" s="25"/>
+      <c r="M21" s="31"/>
       <c r="N21" s="21"/>
-      <c r="O21" s="25"/>
+      <c r="O21" s="31"/>
       <c r="P21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q21" s="25"/>
+      <c r="Q21" s="31"/>
       <c r="R21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S21" s="25"/>
+      <c r="S21" s="31"/>
       <c r="T21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U21" s="25"/>
+      <c r="U21" s="31"/>
     </row>
     <row r="22" ht="43.99" customHeight="1">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
-      <c r="C22" s="27"/>
+      <c r="C22" s="33"/>
       <c r="D22" s="21"/>
-      <c r="E22" s="27"/>
+      <c r="E22" s="33"/>
       <c r="F22" s="21"/>
-      <c r="G22" s="27"/>
+      <c r="G22" s="33"/>
       <c r="H22" s="21"/>
-      <c r="I22" s="27"/>
+      <c r="I22" s="33"/>
       <c r="J22" s="21"/>
-      <c r="K22" s="27"/>
+      <c r="K22" s="33"/>
       <c r="L22" s="21"/>
-      <c r="M22" s="27"/>
+      <c r="M22" s="33"/>
       <c r="N22" s="21"/>
-      <c r="O22" s="27"/>
+      <c r="O22" s="33"/>
       <c r="P22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q22" s="27" t="inlineStr">
+      <c r="Q22" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -7984,7 +8007,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="S22" s="28" t="inlineStr">
+      <c r="S22" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -7994,7 +8017,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U22" s="27" t="inlineStr">
+      <c r="U22" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -8003,37 +8026,37 @@
     <row r="23" ht="43.99" customHeight="1">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
-      <c r="C23" s="22"/>
+      <c r="C23" s="29"/>
       <c r="D23" s="21"/>
-      <c r="E23" s="22"/>
+      <c r="E23" s="29"/>
       <c r="F23" s="21"/>
-      <c r="G23" s="22"/>
+      <c r="G23" s="29"/>
       <c r="H23" s="21"/>
-      <c r="I23" s="22"/>
+      <c r="I23" s="29"/>
       <c r="J23" s="21"/>
-      <c r="K23" s="22"/>
+      <c r="K23" s="29"/>
       <c r="L23" s="21"/>
-      <c r="M23" s="22"/>
+      <c r="M23" s="29"/>
       <c r="N23" s="21"/>
-      <c r="O23" s="22"/>
+      <c r="O23" s="29"/>
       <c r="P23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q23" s="22"/>
+      <c r="Q23" s="29"/>
       <c r="R23" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S23" s="24"/>
+      <c r="S23" s="30"/>
       <c r="T23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U23" s="22" t="inlineStr">
+      <c r="U23" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">후</t>
         </is>
@@ -8042,95 +8065,95 @@
     <row r="24" ht="43.99" customHeight="1">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
-      <c r="C24" s="25"/>
+      <c r="C24" s="31"/>
       <c r="D24" s="21"/>
-      <c r="E24" s="25"/>
+      <c r="E24" s="31"/>
       <c r="F24" s="21"/>
-      <c r="G24" s="25"/>
+      <c r="G24" s="31"/>
       <c r="H24" s="21"/>
-      <c r="I24" s="25"/>
+      <c r="I24" s="31"/>
       <c r="J24" s="21"/>
-      <c r="K24" s="25"/>
+      <c r="K24" s="31"/>
       <c r="L24" s="21"/>
-      <c r="M24" s="25"/>
+      <c r="M24" s="31"/>
       <c r="N24" s="21"/>
-      <c r="O24" s="25"/>
+      <c r="O24" s="31"/>
       <c r="P24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q24" s="25"/>
+      <c r="Q24" s="31"/>
       <c r="R24" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S24" s="26"/>
+      <c r="S24" s="32"/>
       <c r="T24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U24" s="25"/>
+      <c r="U24" s="31"/>
     </row>
     <row r="25" ht="43.99" customHeight="1">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
-      <c r="C25" s="27"/>
+      <c r="C25" s="33"/>
       <c r="D25" s="21"/>
-      <c r="E25" s="27"/>
+      <c r="E25" s="33"/>
       <c r="F25" s="21"/>
-      <c r="G25" s="27"/>
+      <c r="G25" s="33"/>
       <c r="H25" s="21"/>
-      <c r="I25" s="27"/>
+      <c r="I25" s="33"/>
       <c r="J25" s="21"/>
-      <c r="K25" s="27"/>
+      <c r="K25" s="33"/>
       <c r="L25" s="21"/>
-      <c r="M25" s="27"/>
+      <c r="M25" s="33"/>
       <c r="N25" s="21"/>
-      <c r="O25" s="27"/>
+      <c r="O25" s="33"/>
       <c r="P25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q25" s="27"/>
+      <c r="Q25" s="33"/>
       <c r="R25" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑潢</t>
         </is>
       </c>
-      <c r="S25" s="28"/>
+      <c r="S25" s="34"/>
       <c r="T25" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U25" s="28"/>
+      <c r="U25" s="34"/>
     </row>
     <row r="26" ht="43.99" customHeight="1">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
-      <c r="C26" s="22"/>
+      <c r="C26" s="29"/>
       <c r="D26" s="21"/>
-      <c r="E26" s="22"/>
+      <c r="E26" s="29"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="22"/>
+      <c r="G26" s="29"/>
       <c r="H26" s="21"/>
-      <c r="I26" s="22"/>
+      <c r="I26" s="29"/>
       <c r="J26" s="21"/>
-      <c r="K26" s="22"/>
+      <c r="K26" s="29"/>
       <c r="L26" s="21"/>
-      <c r="M26" s="22"/>
+      <c r="M26" s="29"/>
       <c r="N26" s="21"/>
-      <c r="O26" s="22"/>
+      <c r="O26" s="29"/>
       <c r="P26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q26" s="22" t="inlineStr">
+      <c r="Q26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -8140,7 +8163,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S26" s="22" t="inlineStr">
+      <c r="S26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -8150,77 +8173,77 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U26" s="24"/>
+      <c r="U26" s="30"/>
     </row>
     <row r="27" ht="43.99" customHeight="1">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
-      <c r="C27" s="25"/>
+      <c r="C27" s="31"/>
       <c r="D27" s="21"/>
-      <c r="E27" s="25"/>
+      <c r="E27" s="31"/>
       <c r="F27" s="21"/>
-      <c r="G27" s="25"/>
+      <c r="G27" s="31"/>
       <c r="H27" s="21"/>
-      <c r="I27" s="25"/>
+      <c r="I27" s="31"/>
       <c r="J27" s="21"/>
-      <c r="K27" s="25"/>
+      <c r="K27" s="31"/>
       <c r="L27" s="21"/>
-      <c r="M27" s="25"/>
+      <c r="M27" s="31"/>
       <c r="N27" s="21"/>
-      <c r="O27" s="25"/>
+      <c r="O27" s="31"/>
       <c r="P27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q27" s="25"/>
+      <c r="Q27" s="31"/>
       <c r="R27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S27" s="25"/>
+      <c r="S27" s="31"/>
       <c r="T27" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢㳞</t>
         </is>
       </c>
-      <c r="U27" s="26"/>
+      <c r="U27" s="32"/>
     </row>
     <row r="28" ht="43.99" customHeight="1">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
-      <c r="C28" s="27"/>
+      <c r="C28" s="33"/>
       <c r="D28" s="21"/>
-      <c r="E28" s="27"/>
+      <c r="E28" s="33"/>
       <c r="F28" s="21"/>
-      <c r="G28" s="27"/>
+      <c r="G28" s="33"/>
       <c r="H28" s="21"/>
-      <c r="I28" s="27"/>
+      <c r="I28" s="33"/>
       <c r="J28" s="21"/>
-      <c r="K28" s="27"/>
+      <c r="K28" s="33"/>
       <c r="L28" s="21"/>
-      <c r="M28" s="27"/>
+      <c r="M28" s="33"/>
       <c r="N28" s="21"/>
-      <c r="O28" s="27"/>
+      <c r="O28" s="33"/>
       <c r="P28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q28" s="27"/>
+      <c r="Q28" s="33"/>
       <c r="R28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S28" s="27"/>
+      <c r="S28" s="33"/>
       <c r="T28" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U28" s="28"/>
+      <c r="U28" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/sheets/민요/검수/양류가 (채보3).xlsx
+++ b/sheets/민요/검수/양류가 (채보3).xlsx
@@ -392,10 +392,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/양류가 (채보3).xlsx
+++ b/sheets/민요/검수/양류가 (채보3).xlsx
@@ -338,17 +338,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -465,7 +465,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -519,6 +519,46 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2368,314 +2408,314 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="43.01" customHeight="true">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B3" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="18" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B4" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="19"/>
+      <c r="F4" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="I4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="I4" s="19"/>
+    </row>
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B5" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="C5" s="20"/>
+      <c r="D5" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" s="10" t="s">
+      <c r="H5" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="20" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="8" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B6" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="8" t="s">
+      <c r="H6" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B7" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="7" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="H7" s="17"/>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B8" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="D8" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="10" t="s">
+      <c r="H8" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="20" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="8" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B9" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="12" t="s">
+      <c r="D9" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="8" t="s">
+      <c r="H9" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="18" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B10" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="11" t="s">
+      <c r="C10" s="19"/>
+      <c r="D10" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="G10" s="19"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="7" t="s">
+      <c r="C11" s="20"/>
+      <c r="D11" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="7" t="s">
+      <c r="G11" s="20"/>
+      <c r="H11" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="20" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="8" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B12" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" s="8" t="s">
+      <c r="F12" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="9" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B13" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" s="9" t="s">
+      <c r="F13" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="19" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B14" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="20"/>
+      <c r="D14" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="20"/>
+      <c r="H14" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="20" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2685,7 +2725,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="93"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/양류가 (채보3).xlsx
+++ b/sheets/민요/검수/양류가 (채보3).xlsx
@@ -2414,13 +2414,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
   </cols>
   <sheetData>
